--- a/data/constantes.xlsx
+++ b/data/constantes.xlsx
@@ -436,7 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sejour_key</t>
+          <t>id_sejour</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000123</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000098</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000098</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000201</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000077</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sej1</t>
+          <t>ID0000156</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sej0</t>
+          <t>ID0000142</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
